--- a/artfynd/A 48877-2025 artfynd.xlsx
+++ b/artfynd/A 48877-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7120120</v>
+        <v>7120910</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566357.9272216978</v>
+        <v>566358</v>
       </c>
       <c r="R2" t="n">
-        <v>6437907.14277884</v>
+        <v>6437907</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,14 @@
           <t>2011-11-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-11-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32797</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32796</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7120910</v>
+        <v>7120120</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,26 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566357.9272216978</v>
+        <v>566358</v>
       </c>
       <c r="R3" t="n">
-        <v>6437907.14277884</v>
+        <v>6437907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,24 +853,14 @@
           <t>2011-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-11-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32796</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32797</t>
         </is>
       </c>
       <c r="AD3" t="b">
